--- a/artfynd/A 66164-2020 artfynd.xlsx
+++ b/artfynd/A 66164-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 66164-2020 artfynd.xlsx
+++ b/artfynd/A 66164-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY96"/>
+  <dimension ref="A1:AY95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6370,10 +6370,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>72428161</v>
+        <v>72428170</v>
       </c>
       <c r="B50" t="n">
-        <v>95511</v>
+        <v>96354</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6386,21 +6386,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221944</v>
+        <v>221952</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>442584.9097544546</v>
+        <v>442770.1897952924</v>
       </c>
       <c r="R50" t="n">
-        <v>7164259.026555047</v>
+        <v>7164255.097932017</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6486,10 +6486,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>72428170</v>
+        <v>72428135</v>
       </c>
       <c r="B51" t="n">
-        <v>96354</v>
+        <v>73698</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6498,25 +6498,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>1467</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6526,10 +6526,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>442770.1897952924</v>
+        <v>442830.0719238349</v>
       </c>
       <c r="R51" t="n">
-        <v>7164255.097932017</v>
+        <v>7164329.135065884</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6602,10 +6602,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>72428135</v>
+        <v>72428143</v>
       </c>
       <c r="B52" t="n">
-        <v>73698</v>
+        <v>76863</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6614,25 +6614,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1467</v>
+        <v>498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6642,10 +6642,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>442830.0719238349</v>
+        <v>442835.7847200944</v>
       </c>
       <c r="R52" t="n">
-        <v>7164329.135065884</v>
+        <v>7164426.954739005</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6718,10 +6718,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>72428143</v>
+        <v>72428145</v>
       </c>
       <c r="B53" t="n">
-        <v>76863</v>
+        <v>81236</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6730,25 +6730,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>498</v>
+        <v>1312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6758,10 +6758,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>442835.7847200944</v>
+        <v>442835.8076917675</v>
       </c>
       <c r="R53" t="n">
-        <v>7164426.954739005</v>
+        <v>7164451.006137197</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6834,10 +6834,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>72428145</v>
+        <v>72428132</v>
       </c>
       <c r="B54" t="n">
-        <v>81236</v>
+        <v>77506</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6850,21 +6850,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6874,10 +6874,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>442835.8076917675</v>
+        <v>442649.9223493547</v>
       </c>
       <c r="R54" t="n">
-        <v>7164451.006137197</v>
+        <v>7164240.186953428</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6939,7 +6939,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elin Götmark, Sofia Lundell, Carin von Köhler</t>
+          <t>Elin Götmark, Lars Gerre</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6950,10 +6950,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>72428132</v>
+        <v>72428185</v>
       </c>
       <c r="B55" t="n">
-        <v>77506</v>
+        <v>95519</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6962,25 +6962,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6990,10 +6990,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>442649.9223493547</v>
+        <v>442861.9764822281</v>
       </c>
       <c r="R55" t="n">
-        <v>7164240.186953428</v>
+        <v>7164401.980021957</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Elin Götmark, Lars Gerre</t>
+          <t>Elin Götmark, Sofia Lundell, Carin von Köhler</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -7066,10 +7066,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>72428185</v>
+        <v>72428177</v>
       </c>
       <c r="B56" t="n">
-        <v>95519</v>
+        <v>85703</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7078,25 +7078,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221945</v>
+        <v>510</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7106,10 +7106,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>442861.9764822281</v>
+        <v>442713.9126088183</v>
       </c>
       <c r="R56" t="n">
-        <v>7164401.980021957</v>
+        <v>7164281.071816676</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7182,10 +7182,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>72428177</v>
+        <v>72428138</v>
       </c>
       <c r="B57" t="n">
-        <v>85703</v>
+        <v>94121</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7198,21 +7198,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>510</v>
+        <v>53</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7222,10 +7222,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>442713.9126088183</v>
+        <v>442844.8081798108</v>
       </c>
       <c r="R57" t="n">
-        <v>7164281.071816676</v>
+        <v>7164358.06424012</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7298,10 +7298,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>72428138</v>
+        <v>72428129</v>
       </c>
       <c r="B58" t="n">
-        <v>94121</v>
+        <v>56540</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7314,21 +7314,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>442844.8081798108</v>
+        <v>442675.0431469103</v>
       </c>
       <c r="R58" t="n">
-        <v>7164358.06424012</v>
+        <v>7164295.120768967</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7403,7 +7403,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Elin Götmark, Sofia Lundell, Carin von Köhler</t>
+          <t>Elin Götmark, Lars Gerre</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -7414,10 +7414,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>72428129</v>
+        <v>72428175</v>
       </c>
       <c r="B59" t="n">
-        <v>56540</v>
+        <v>89392</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7430,21 +7430,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7454,10 +7454,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>442675.0431469103</v>
+        <v>442685.2147472691</v>
       </c>
       <c r="R59" t="n">
-        <v>7164295.120768967</v>
+        <v>7164287.197342045</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Elin Götmark, Lars Gerre</t>
+          <t>Elin Götmark, Sofia Lundell, Carin von Köhler</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7530,10 +7530,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>72428175</v>
+        <v>72428230</v>
       </c>
       <c r="B60" t="n">
-        <v>89392</v>
+        <v>89410</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7546,21 +7546,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7570,10 +7570,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>442685.2147472691</v>
+        <v>442587.5389925711</v>
       </c>
       <c r="R60" t="n">
-        <v>7164287.197342045</v>
+        <v>7164307.083111782</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7635,7 +7635,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Elin Götmark, Sofia Lundell, Carin von Köhler</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7646,10 +7646,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>72428230</v>
+        <v>72428179</v>
       </c>
       <c r="B61" t="n">
-        <v>89410</v>
+        <v>73678</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7658,25 +7658,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7686,10 +7686,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>442587.5389925711</v>
+        <v>442850.8832096329</v>
       </c>
       <c r="R61" t="n">
-        <v>7164307.083111782</v>
+        <v>7164360.95640328</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7751,7 +7751,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Elin Götmark, Sofia Lundell, Carin von Köhler</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7762,10 +7762,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>72428179</v>
+        <v>72428162</v>
       </c>
       <c r="B62" t="n">
-        <v>73678</v>
+        <v>92501</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7778,21 +7778,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6439</v>
+        <v>1004672</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Källmossor</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Philonotis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Brid.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7802,10 +7802,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>442850.8832096329</v>
+        <v>442584.9097544546</v>
       </c>
       <c r="R62" t="n">
-        <v>7164360.95640328</v>
+        <v>7164259.026555047</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7878,10 +7878,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>72428162</v>
+        <v>72428125</v>
       </c>
       <c r="B63" t="n">
-        <v>92501</v>
+        <v>81236</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7890,25 +7890,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1004672</v>
+        <v>1312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7918,10 +7918,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>442584.9097544546</v>
+        <v>442685.8156937378</v>
       </c>
       <c r="R63" t="n">
-        <v>7164259.026555047</v>
+        <v>7164205.146707136</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7966,6 +7966,11 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>gammal granbark</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7974,6 +7979,11 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AS63" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7983,7 +7993,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Elin Götmark, Sofia Lundell, Carin von Köhler</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7994,10 +8004,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>72428125</v>
+        <v>72428182</v>
       </c>
       <c r="B64" t="n">
-        <v>81236</v>
+        <v>96251</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8006,25 +8016,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1312</v>
+        <v>219790</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8034,10 +8044,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>442685.8156937378</v>
+        <v>442835.8008932495</v>
       </c>
       <c r="R64" t="n">
-        <v>7164205.146707136</v>
+        <v>7164427.813431622</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8082,11 +8092,6 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>gammal granbark</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8095,11 +8100,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AS64" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Elin Götmark, Sofia Lundell, Carin von Köhler</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -8120,10 +8120,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>72428182</v>
+        <v>72428174</v>
       </c>
       <c r="B65" t="n">
-        <v>96251</v>
+        <v>73698</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8132,25 +8132,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219790</v>
+        <v>1467</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8160,10 +8160,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>442835.8008932495</v>
+        <v>442836.8936010334</v>
       </c>
       <c r="R65" t="n">
-        <v>7164427.813431622</v>
+        <v>7164325.999993176</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8225,7 +8225,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Elin Götmark, Sofia Lundell, Carin von Köhler</t>
+          <t>Elin Götmark, Sofia Lundell, Carin von Köhler, Bo karlstens</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -8236,10 +8236,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>72428174</v>
+        <v>72428181</v>
       </c>
       <c r="B66" t="n">
-        <v>73698</v>
+        <v>78596</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8248,25 +8248,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1467</v>
+        <v>6462</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8276,10 +8276,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>442836.8936010334</v>
+        <v>442850.8832096329</v>
       </c>
       <c r="R66" t="n">
-        <v>7164325.999993176</v>
+        <v>7164360.95640328</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8341,7 +8341,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Elin Götmark, Sofia Lundell, Carin von Köhler, Bo karlstens</t>
+          <t>Elin Götmark, Sofia Lundell, Carin von Köhler</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -8352,10 +8352,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>72428181</v>
+        <v>72428141</v>
       </c>
       <c r="B67" t="n">
-        <v>78596</v>
+        <v>77756</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8368,21 +8368,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6462</v>
+        <v>6459</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8392,10 +8392,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>442850.8832096329</v>
+        <v>442858.8717773175</v>
       </c>
       <c r="R67" t="n">
-        <v>7164360.95640328</v>
+        <v>7164374.120710684</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8468,10 +8468,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>72428141</v>
+        <v>72428153</v>
       </c>
       <c r="B68" t="n">
-        <v>77756</v>
+        <v>92688</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8484,21 +8484,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6459</v>
+        <v>2387</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8508,10 +8508,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>442858.8717773175</v>
+        <v>442584.9097544546</v>
       </c>
       <c r="R68" t="n">
-        <v>7164374.120710684</v>
+        <v>7164259.026555047</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8584,10 +8584,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>72428153</v>
+        <v>72428152</v>
       </c>
       <c r="B69" t="n">
-        <v>92688</v>
+        <v>76863</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8596,25 +8596,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2387</v>
+        <v>498</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8624,10 +8624,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>442584.9097544546</v>
+        <v>442841.8838797714</v>
       </c>
       <c r="R69" t="n">
-        <v>7164259.026555047</v>
+        <v>7164431.134853273</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8700,10 +8700,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>72428152</v>
+        <v>72428183</v>
       </c>
       <c r="B70" t="n">
-        <v>76863</v>
+        <v>96354</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8712,25 +8712,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>498</v>
+        <v>221952</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8740,10 +8740,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>442841.8838797714</v>
+        <v>442835.8008932495</v>
       </c>
       <c r="R70" t="n">
-        <v>7164431.134853273</v>
+        <v>7164427.813431622</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8816,10 +8816,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>72428183</v>
+        <v>72428150</v>
       </c>
       <c r="B71" t="n">
-        <v>96354</v>
+        <v>77506</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8828,25 +8828,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8856,10 +8856,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>442835.8008932495</v>
+        <v>442837.1254819586</v>
       </c>
       <c r="R71" t="n">
-        <v>7164427.813431622</v>
+        <v>7164383.979316522</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8932,10 +8932,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>72428150</v>
+        <v>72428133</v>
       </c>
       <c r="B72" t="n">
-        <v>77506</v>
+        <v>89406</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8948,21 +8948,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8972,10 +8972,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>442837.1254819586</v>
+        <v>442737.9077428806</v>
       </c>
       <c r="R72" t="n">
-        <v>7164383.979316522</v>
+        <v>7164208.029307944</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9048,10 +9048,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>72428133</v>
+        <v>72428147</v>
       </c>
       <c r="B73" t="n">
-        <v>89406</v>
+        <v>89392</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9064,21 +9064,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9088,10 +9088,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>442737.9077428806</v>
+        <v>442683.0976865327</v>
       </c>
       <c r="R73" t="n">
-        <v>7164208.029307944</v>
+        <v>7164288.955396261</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9164,10 +9164,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>72428147</v>
+        <v>72428139</v>
       </c>
       <c r="B74" t="n">
-        <v>89392</v>
+        <v>76863</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9176,25 +9176,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9204,10 +9204,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>442683.0976865327</v>
+        <v>442850.1310160412</v>
       </c>
       <c r="R74" t="n">
-        <v>7164288.955396261</v>
+        <v>7164458.037804305</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9280,10 +9280,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>72428139</v>
+        <v>72442450</v>
       </c>
       <c r="B75" t="n">
-        <v>76863</v>
+        <v>73693</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9292,38 +9292,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>498</v>
+        <v>6440</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Högsätern västra, Jmt</t>
+          <t>Högsätern syd, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>442850.1310160412</v>
+        <v>442888.8974857909</v>
       </c>
       <c r="R75" t="n">
-        <v>7164458.037804305</v>
+        <v>7164392.883280552</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9377,15 +9377,20 @@
       <c r="AG75" t="b">
         <v>0</v>
       </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Barbara Kühn</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Elin Götmark, Sofia Lundell, Carin von Köhler</t>
+          <t>Barbara Kühn</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -9396,7 +9401,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>72442450</v>
+        <v>72442448</v>
       </c>
       <c r="B76" t="n">
         <v>73693</v>
@@ -9436,10 +9441,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>442888.8974857909</v>
+        <v>442935.9385430831</v>
       </c>
       <c r="R76" t="n">
-        <v>7164392.883280552</v>
+        <v>7164333.155998505</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9517,10 +9522,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>72442448</v>
+        <v>72442449</v>
       </c>
       <c r="B77" t="n">
-        <v>73693</v>
+        <v>76490</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9533,21 +9538,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9557,10 +9562,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>442935.9385430831</v>
+        <v>442888.8974857909</v>
       </c>
       <c r="R77" t="n">
-        <v>7164333.155998505</v>
+        <v>7164392.883280552</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9638,10 +9643,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>72442449</v>
+        <v>72442451</v>
       </c>
       <c r="B78" t="n">
-        <v>76490</v>
+        <v>73693</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9654,21 +9659,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9678,10 +9683,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>442888.8974857909</v>
+        <v>442825.9298612036</v>
       </c>
       <c r="R78" t="n">
-        <v>7164392.883280552</v>
+        <v>7164428.858361945</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9759,10 +9764,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>72442451</v>
+        <v>72478769</v>
       </c>
       <c r="B79" t="n">
-        <v>73693</v>
+        <v>77668</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9771,38 +9776,40 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6440</v>
+        <v>1249</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Högsätern syd, Jmt</t>
+          <t>Högsätern västra, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>442825.9298612036</v>
+        <v>442703.7989789512</v>
       </c>
       <c r="R79" t="n">
-        <v>7164428.858361945</v>
+        <v>7164200.941414273</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9853,23 +9860,49 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
-      <c r="AS79" t="inlineStr">
-        <is>
-          <t>Bjarne Tutturen</t>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>naturskog</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AL79" t="inlineStr">
+        <is>
+          <t>grov björk</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Betula # grov björk</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Barbara Kühn</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Barbara Kühn</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -9880,10 +9913,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>72478769</v>
+        <v>72478633</v>
       </c>
       <c r="B80" t="n">
-        <v>77668</v>
+        <v>77506</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9892,25 +9925,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9922,10 +9955,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>442703.7989789512</v>
+        <v>442662.9735457325</v>
       </c>
       <c r="R80" t="n">
-        <v>7164200.941414273</v>
+        <v>7164339.159294136</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9985,29 +10018,19 @@
           <t>Högörtgranskog</t>
         </is>
       </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>naturskog</t>
-        </is>
-      </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AL80" t="inlineStr">
-        <is>
-          <t>grov björk</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Betula # grov björk</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10029,10 +10052,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>72478633</v>
+        <v>72478674</v>
       </c>
       <c r="B81" t="n">
-        <v>77506</v>
+        <v>73693</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10045,21 +10068,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10071,10 +10094,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>442662.9735457325</v>
+        <v>442671.1414802122</v>
       </c>
       <c r="R81" t="n">
-        <v>7164339.159294136</v>
+        <v>7164339.005005565</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10132,6 +10155,11 @@
       <c r="AH81" t="inlineStr">
         <is>
           <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>naturskog</t>
         </is>
       </c>
       <c r="AJ81" t="inlineStr">
@@ -10168,10 +10196,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>72478674</v>
+        <v>72478807</v>
       </c>
       <c r="B82" t="n">
-        <v>73693</v>
+        <v>77668</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10180,25 +10208,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6440</v>
+        <v>1249</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10210,10 +10238,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>442671.1414802122</v>
+        <v>442633.9432065043</v>
       </c>
       <c r="R82" t="n">
-        <v>7164339.005005565</v>
+        <v>7164282.152666167</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10290,7 +10318,7 @@
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>död gran # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10312,10 +10340,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>72478807</v>
+        <v>72654961</v>
       </c>
       <c r="B83" t="n">
-        <v>77668</v>
+        <v>76863</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10328,21 +10356,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1249</v>
+        <v>498</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10350,17 +10378,17 @@
       <c r="K83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Högsätern västra, Jmt</t>
+          <t>Högsätern v, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>442633.9432065043</v>
+        <v>442811.742764472</v>
       </c>
       <c r="R83" t="n">
-        <v>7164282.152666167</v>
+        <v>7164451.888986105</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10414,52 +10442,33 @@
       </c>
       <c r="AH83" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>naturskog</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>död gran # Picea abies</t>
+          <t>Grandominerad blandskog</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
-        </is>
-      </c>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>72654961</v>
+        <v>72654974</v>
       </c>
       <c r="B84" t="n">
-        <v>76863</v>
+        <v>76490</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10468,25 +10477,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>498</v>
+        <v>228579</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10581,10 +10590,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>72654974</v>
+        <v>72655123</v>
       </c>
       <c r="B85" t="n">
-        <v>76490</v>
+        <v>96354</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10593,40 +10602,46 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228579</v>
+        <v>221952</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Högsätern v, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>442811.742764472</v>
+        <v>442798.923400846</v>
       </c>
       <c r="R85" t="n">
-        <v>7164451.888986105</v>
+        <v>7164364.941762218</v>
       </c>
       <c r="S85" t="n">
         <v>50</v>
@@ -10706,10 +10721,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>72655123</v>
+        <v>72655205</v>
       </c>
       <c r="B86" t="n">
-        <v>96354</v>
+        <v>77668</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10718,49 +10733,43 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221952</v>
+        <v>1249</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Högsätern v, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>442798.923400846</v>
+        <v>442712.2906492247</v>
       </c>
       <c r="R86" t="n">
-        <v>7164364.941762218</v>
+        <v>7164263.492059365</v>
       </c>
       <c r="S86" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10837,10 +10846,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>72655205</v>
+        <v>72654959</v>
       </c>
       <c r="B87" t="n">
-        <v>77668</v>
+        <v>96354</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10849,43 +10858,49 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1249</v>
+        <v>221952</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Högsätern v, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>442712.2906492247</v>
+        <v>442811.742764472</v>
       </c>
       <c r="R87" t="n">
-        <v>7164263.492059365</v>
+        <v>7164451.888986105</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10962,10 +10977,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>72654959</v>
+        <v>72655019</v>
       </c>
       <c r="B88" t="n">
-        <v>96354</v>
+        <v>89410</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10974,36 +10989,30 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Högsätern v, Jmt</t>
@@ -11093,10 +11102,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>72655019</v>
+        <v>72654986</v>
       </c>
       <c r="B89" t="n">
-        <v>89410</v>
+        <v>96943</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11105,30 +11114,32 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5432</v>
+        <v>222302</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Högsätern v, Jmt</t>
@@ -11218,57 +11229,53 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>72654986</v>
+        <v>72428146</v>
       </c>
       <c r="B90" t="n">
-        <v>96943</v>
+        <v>56395</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>222302</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Högsätern v, Jmt</t>
+          <t>Högsätern västra, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>442811.742764472</v>
+        <v>442584.0998256491</v>
       </c>
       <c r="R90" t="n">
-        <v>7164451.888986105</v>
+        <v>7164307.148167289</v>
       </c>
       <c r="S90" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11310,42 +11317,40 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>Grandominerad blandskog</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr"/>
+          <t>Elin Götmark, Sofia Lundell, Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>72428146</v>
+        <v>72428225</v>
       </c>
       <c r="B91" t="n">
         <v>56395</v>
@@ -11385,10 +11390,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>442584.0998256491</v>
+        <v>442601.6768390124</v>
       </c>
       <c r="R91" t="n">
-        <v>7164307.148167289</v>
+        <v>7164304.23861715</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11435,7 +11440,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>hack</t>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11455,7 +11460,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Elin Götmark, Sofia Lundell, Carin von Köhler</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -11466,7 +11471,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>72428225</v>
+        <v>72428226</v>
       </c>
       <c r="B92" t="n">
         <v>56395</v>
@@ -11506,10 +11511,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>442601.6768390124</v>
+        <v>442728.8699733776</v>
       </c>
       <c r="R92" t="n">
-        <v>7164304.23861715</v>
+        <v>7164276.064830386</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11587,7 +11592,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>72428226</v>
+        <v>72442453</v>
       </c>
       <c r="B93" t="n">
         <v>56395</v>
@@ -11621,16 +11626,20 @@
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Högsätern västra, Jmt</t>
+          <t>Högsätern syd, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>442728.8699733776</v>
+        <v>442914.1351857039</v>
       </c>
       <c r="R93" t="n">
-        <v>7164276.064830386</v>
+        <v>7164340.0086639</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11677,7 +11686,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Hackmärken</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11688,16 +11697,21 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Barbara Kühn</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Barbara Kühn</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -11708,7 +11722,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>72442453</v>
+        <v>72442454</v>
       </c>
       <c r="B94" t="n">
         <v>56395</v>
@@ -11752,10 +11766,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>442914.1351857039</v>
+        <v>442853.1510580257</v>
       </c>
       <c r="R94" t="n">
-        <v>7164340.0086639</v>
+        <v>7164412.883713395</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11838,7 +11852,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>72442454</v>
+        <v>72428130</v>
       </c>
       <c r="B95" t="n">
         <v>56395</v>
@@ -11872,20 +11886,16 @@
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Högsätern syd, Jmt</t>
+          <t>Högsätern västra, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>442853.1510580257</v>
+        <v>442675.0431469103</v>
       </c>
       <c r="R95" t="n">
-        <v>7164412.883713395</v>
+        <v>7164295.120768967</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11932,7 +11942,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>hack på två granar</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11943,145 +11953,19 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AS95" t="inlineStr">
-        <is>
-          <t>Bjarne Tutturen</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Barbara Kühn</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Barbara Kühn</t>
+          <t>Elin Götmark, Lars Gerre</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>72428130</v>
-      </c>
-      <c r="B96" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E96" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>Högsätern västra, Jmt</t>
-        </is>
-      </c>
-      <c r="Q96" t="n">
-        <v>442675.0431469103</v>
-      </c>
-      <c r="R96" t="n">
-        <v>7164295.120768967</v>
-      </c>
-      <c r="S96" t="n">
-        <v>10</v>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>Frostviken</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>2018-07-24</t>
-        </is>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>2018-07-24</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>hack på två granar</t>
-        </is>
-      </c>
-      <c r="AD96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT96" t="inlineStr"/>
-      <c r="AW96" t="inlineStr">
-        <is>
-          <t>Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>Elin Götmark, Lars Gerre</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
